--- a/artfynd/A 32328-2024 artfynd.xlsx
+++ b/artfynd/A 32328-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123321759</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123321761</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 32328-2024 artfynd.xlsx
+++ b/artfynd/A 32328-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321759</v>
+        <v>123321761</v>
       </c>
       <c r="B2" t="n">
         <v>57497</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607432</v>
+        <v>607412</v>
       </c>
       <c r="R2" t="n">
-        <v>6751665</v>
+        <v>6751747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_174</t>
+          <t>2024_172</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -810,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321761</v>
+        <v>123321759</v>
       </c>
       <c r="B3" t="n">
         <v>57497</v>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607412</v>
+        <v>607432</v>
       </c>
       <c r="R3" t="n">
-        <v>6751747</v>
+        <v>6751665</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_172</t>
+          <t>2024_174</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 32328-2024 artfynd.xlsx
+++ b/artfynd/A 32328-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321761</v>
+        <v>123321759</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607412</v>
+        <v>607432</v>
       </c>
       <c r="R2" t="n">
-        <v>6751747</v>
+        <v>6751665</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_172</t>
+          <t>2024_174</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321759</v>
+        <v>123321761</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607432</v>
+        <v>607412</v>
       </c>
       <c r="R3" t="n">
-        <v>6751665</v>
+        <v>6751747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_174</t>
+          <t>2024_172</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 32328-2024 artfynd.xlsx
+++ b/artfynd/A 32328-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321759</v>
+        <v>123321761</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607432</v>
+        <v>607412</v>
       </c>
       <c r="R2" t="n">
-        <v>6751665</v>
+        <v>6751747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_174</t>
+          <t>2024_172</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321761</v>
+        <v>123321759</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607412</v>
+        <v>607432</v>
       </c>
       <c r="R3" t="n">
-        <v>6751747</v>
+        <v>6751665</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_172</t>
+          <t>2024_174</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 32328-2024 artfynd.xlsx
+++ b/artfynd/A 32328-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321761</v>
+        <v>123321759</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607412</v>
+        <v>607432</v>
       </c>
       <c r="R2" t="n">
-        <v>6751747</v>
+        <v>6751665</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_172</t>
+          <t>2024_174</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321759</v>
+        <v>123321761</v>
       </c>
       <c r="B3" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607432</v>
+        <v>607412</v>
       </c>
       <c r="R3" t="n">
-        <v>6751665</v>
+        <v>6751747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_174</t>
+          <t>2024_172</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 32328-2024 artfynd.xlsx
+++ b/artfynd/A 32328-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321759</v>
+        <v>123321761</v>
       </c>
       <c r="B2" t="n">
         <v>57507</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607432</v>
+        <v>607412</v>
       </c>
       <c r="R2" t="n">
-        <v>6751665</v>
+        <v>6751747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_174</t>
+          <t>2024_172</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -810,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321761</v>
+        <v>123321759</v>
       </c>
       <c r="B3" t="n">
         <v>57507</v>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607412</v>
+        <v>607432</v>
       </c>
       <c r="R3" t="n">
-        <v>6751747</v>
+        <v>6751665</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_172</t>
+          <t>2024_174</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 32328-2024 artfynd.xlsx
+++ b/artfynd/A 32328-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321761</v>
+        <v>123321759</v>
       </c>
       <c r="B2" t="n">
         <v>57507</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607412</v>
+        <v>607432</v>
       </c>
       <c r="R2" t="n">
-        <v>6751747</v>
+        <v>6751665</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_172</t>
+          <t>2024_174</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -810,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321759</v>
+        <v>123321761</v>
       </c>
       <c r="B3" t="n">
         <v>57507</v>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607432</v>
+        <v>607412</v>
       </c>
       <c r="R3" t="n">
-        <v>6751665</v>
+        <v>6751747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_174</t>
+          <t>2024_172</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 32328-2024 artfynd.xlsx
+++ b/artfynd/A 32328-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>123321759</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -813,16 +808,11 @@
         <v>123321761</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -938,6 +928,136 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123321762</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hagsta, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>607403</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6751762</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hamrånge</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2024_170</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>orrspillning tarmtömning</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ofir Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 32328-2024 artfynd.xlsx
+++ b/artfynd/A 32328-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321759</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -932,6 +942,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321761</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1062,8 +1077,18 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321762</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>